--- a/processo_2/synthetic_proposals/PROPOSTA_013/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_013/ficha_pontuacao.xlsx
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,17 +749,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -799,16 +799,8 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4362-4833</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -853,13 +845,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -939,13 +931,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
@@ -958,17 +950,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
@@ -981,7 +973,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1050,7 +1042,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1075,7 +1067,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1118,7 +1110,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1141,7 +1133,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1168,13 +1160,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>20</v>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
@@ -1187,7 +1179,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1210,7 +1202,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1233,7 +1225,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1256,17 +1248,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1279,17 +1271,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
@@ -1302,7 +1294,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1325,17 +1317,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>1.5</v>
       </c>
       <c r="F43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
@@ -1415,13 +1407,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1438,13 +1430,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr"/>
     </row>
@@ -1484,13 +1476,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G50" t="inlineStr"/>
     </row>
@@ -1543,7 +1535,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1566,7 +1558,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1612,17 +1604,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1635,7 +1627,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1660,7 +1652,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>56.5</v>
+        <v>15</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1707,13 +1699,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
         <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
@@ -1843,7 +1835,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1858,7 +1850,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
